--- a/excel tasks logical formating.xlsx
+++ b/excel tasks logical formating.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC11\Desktop\vansh\Exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFA7F1F-D6F6-4641-B373-0A264DC81F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD474B77-F213-4377-AA39-EA2C6ABAD645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{D604C0F3-70FD-4EE8-8C56-19CAD7AFDC7B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{D604C0F3-70FD-4EE8-8C56-19CAD7AFDC7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet6" sheetId="6" r:id="rId5"/>
-    <sheet name="Sheet7" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet8" sheetId="8" r:id="rId7"/>
-    <sheet name="Sheet9" sheetId="9" r:id="rId8"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId9"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet8" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet9" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet10" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="55">
   <si>
     <t>Roll No</t>
   </si>
@@ -289,6 +290,37 @@
 Task
 Divide Number 1 by Number 2
 If error → show "Invalid"</t>
+  </si>
+  <si>
+    <t>Targets Achieved</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
+    <t>Raj</t>
+  </si>
+  <si>
+    <t>Sunita</t>
+  </si>
+  <si>
+    <t>Manoj</t>
+  </si>
+  <si>
+    <t>Kavita</t>
+  </si>
+  <si>
+    <t>Task 10: Performance Evaluation (Combined Logic)
+Dataset
+Employee Name	Targets Achieved	Attendance %	Performance
+Raj	45	92	
+Sunita	38	85	
+Manoj	50	95	
+Kavita	30	70	
+Task
+Attendance ≥ 90 AND Targets ≥ 40 → Excellent
+Attendance ≥ 80 → Good
+Else → Needs Improvement</t>
   </si>
 </sst>
 </file>
@@ -895,6 +927,428 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115B3FBE-D147-4CFC-88F5-7ECB599919CD}">
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" ht="69.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2">
+        <v>92</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <f>IF(AND(C2&gt;=90,B2&gt;=40),"Excellent",IF(C2&gt;=80,"Good","Need Improvement"))</f>
+        <v>Excellent</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3">
+        <v>85</v>
+      </c>
+      <c r="D3" s="2" t="str">
+        <f t="shared" ref="D3:D5" si="0">IF(AND(C3&gt;=90,B3&gt;=40),"Excellent",IF(C3&gt;=80,"Good","Need Improvement"))</f>
+        <v>Good</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="2">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>95</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Excellent</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3">
+        <v>70</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Need Improvement</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J8" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="8"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+    </row>
+    <row r="17" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="8"/>
+      <c r="T17" s="8"/>
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+    </row>
+    <row r="18" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+    </row>
+    <row r="19" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+    </row>
+    <row r="20" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+    </row>
+    <row r="21" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="8"/>
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+    </row>
+    <row r="22" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+    </row>
+    <row r="23" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="8"/>
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+    </row>
+    <row r="24" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+    </row>
+    <row r="25" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="8"/>
+      <c r="Q25" s="8"/>
+      <c r="R25" s="8"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="8"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+    </row>
+    <row r="26" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+    </row>
+    <row r="27" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
+      <c r="N27" s="8"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="8"/>
+      <c r="Q27" s="8"/>
+      <c r="R27" s="8"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="8"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+    </row>
+    <row r="28" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+    </row>
+    <row r="29" spans="10:22" x14ac:dyDescent="0.25">
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="8"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="J8:V29"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AC35669-BBEA-44F5-A4C2-BD5EB4160454}">
   <dimension ref="A1:P17"/>
@@ -1512,6 +1966,297 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F67F9C20-5FAA-420C-B392-5905B4E87BF7}">
+  <dimension ref="A1:R23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:18" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2">
+        <f>IFERROR(A2/B2,"Invalid")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f t="shared" ref="C3:C6" si="0">IFERROR(A3/B3,"Invalid")</f>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="2"/>
+      <c r="I6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+    </row>
+    <row r="17" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+    </row>
+    <row r="18" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+    </row>
+    <row r="19" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+    </row>
+    <row r="20" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+    </row>
+    <row r="21" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="8"/>
+      <c r="R21" s="8"/>
+    </row>
+    <row r="22" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+    </row>
+    <row r="23" spans="9:18" x14ac:dyDescent="0.25">
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="8"/>
+      <c r="R23" s="8"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I6:R23"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4599039C-AEDA-45C9-AFAB-5050023C4219}">
   <dimension ref="A1:Q23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1859,7 +2604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FD8F193-2981-4BC4-8C13-E2AA9CDC46BE}">
   <dimension ref="A1:S28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2261,7 +3006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F907E50-AE8C-447F-803A-F115894FCA6C}">
   <dimension ref="A1:T23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2620,7 +3365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF961337-FCD5-4853-ABE0-AE0879BE88F5}">
   <dimension ref="A1:S21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2972,7 +3717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86CA3956-1C93-4CA8-B3FC-2FA9F74C3D46}">
   <dimension ref="A1:U28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3320,295 +4065,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F67F9C20-5FAA-420C-B392-5905B4E87BF7}">
-  <dimension ref="A1:R23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:18" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2">
-        <f>IFERROR(A2/B2,"Invalid")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <f t="shared" ref="C3:C6" si="0">IFERROR(A3/B3,"Invalid")</f>
-        <v>Invalid</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>20</v>
-      </c>
-      <c r="B4" s="2">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Invalid</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="2"/>
-      <c r="I6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-    </row>
-    <row r="17" spans="9:18" x14ac:dyDescent="0.25">
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-    </row>
-    <row r="18" spans="9:18" x14ac:dyDescent="0.25">
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-    </row>
-    <row r="19" spans="9:18" x14ac:dyDescent="0.25">
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-    </row>
-    <row r="20" spans="9:18" x14ac:dyDescent="0.25">
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-    </row>
-    <row r="21" spans="9:18" x14ac:dyDescent="0.25">
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-    </row>
-    <row r="22" spans="9:18" x14ac:dyDescent="0.25">
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-    </row>
-    <row r="23" spans="9:18" x14ac:dyDescent="0.25">
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="I6:R23"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>